--- a/Mecanica/M33.xlsx
+++ b/Mecanica/M33.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\Practicas-Fisica\Mecanica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80526994-92D2-436D-9270-83B0A74C6785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261095BE-D9B9-49C8-A93B-64C03FC59006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30507091-A365-4BAF-81AB-92C407D8FAA8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12096" xr2:uid="{30507091-A365-4BAF-81AB-92C407D8FAA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -536,7 +536,7 @@
         <v>13.26</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I50" si="0">ROW()*0.5-1</f>
+        <f t="shared" ref="I4:I64" si="0">ROW()*0.5-1</f>
         <v>1</v>
       </c>
     </row>
@@ -1050,6 +1050,7 @@
         <v>3.6266666666666665</v>
       </c>
       <c r="I51">
+        <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
     </row>
@@ -1059,7 +1060,8 @@
         <v>4.2600000000000007</v>
       </c>
       <c r="I52">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="8:9" x14ac:dyDescent="0.3">
@@ -1068,7 +1070,8 @@
         <v>1.9033333333333333</v>
       </c>
       <c r="I53">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>25.5</v>
       </c>
     </row>
     <row r="54" spans="8:9" x14ac:dyDescent="0.3">
@@ -1077,7 +1080,8 @@
         <v>2.7766666666666668</v>
       </c>
       <c r="I54">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="8:9" x14ac:dyDescent="0.3">
@@ -1086,7 +1090,8 @@
         <v>2.5166666666666671</v>
       </c>
       <c r="I55">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>26.5</v>
       </c>
     </row>
     <row r="56" spans="8:9" x14ac:dyDescent="0.3">
@@ -1095,7 +1100,8 @@
         <v>1.05</v>
       </c>
       <c r="I56">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="8:9" x14ac:dyDescent="0.3">
@@ -1104,7 +1110,8 @@
         <v>1.31</v>
       </c>
       <c r="I57">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>27.5</v>
       </c>
     </row>
     <row r="58" spans="8:9" x14ac:dyDescent="0.3">
@@ -1113,7 +1120,8 @@
         <v>0.85000000000000009</v>
       </c>
       <c r="I58">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="8:9" x14ac:dyDescent="0.3">
@@ -1122,7 +1130,8 @@
         <v>1.9466666666666665</v>
       </c>
       <c r="I59">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>28.5</v>
       </c>
     </row>
     <row r="60" spans="8:9" x14ac:dyDescent="0.3">
@@ -1131,7 +1140,8 @@
         <v>2.2866666666666666</v>
       </c>
       <c r="I60">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="8:9" x14ac:dyDescent="0.3">
@@ -1140,7 +1150,8 @@
         <v>1.5133333333333334</v>
       </c>
       <c r="I61">
-        <v>24.5</v>
+        <f t="shared" si="0"/>
+        <v>29.5</v>
       </c>
     </row>
     <row r="62" spans="8:9" x14ac:dyDescent="0.3">
@@ -1148,20 +1159,33 @@
         <f>AVERAGE(6.61,11.05,8.25)</f>
         <v>8.6366666666666667</v>
       </c>
+      <c r="I62">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="63" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H63">
         <f>AVERAGE(8.19,8.55,14.78)</f>
         <v>10.506666666666668</v>
       </c>
+      <c r="I63">
+        <f t="shared" si="0"/>
+        <v>30.5</v>
+      </c>
     </row>
     <row r="64" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H64">
         <f>AVERAGE(10.28,7.48,4.68)</f>
         <v>7.4799999999999995</v>
       </c>
+      <c r="I64">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>